--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_267_R27.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_267_R27.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5817</v>
+        <v>3.5555</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6236</v>
+        <v>4.6983</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0419</v>
+        <v>-1.1427</v>
       </c>
       <c r="G2" t="n">
         <v>0.1875</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>0.322</v>
+        <v>0.2959</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0395</v>
+        <v>0.1142</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2825</v>
+        <v>0.1817</v>
       </c>
       <c r="V2" t="n">
         <v>2.1444</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1741</v>
+        <v>2.1622</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9575</v>
+        <v>0.9456</v>
       </c>
       <c r="F3" t="n">
         <v>1.2166</v>
@@ -688,10 +688,10 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2987</v>
+        <v>0.2869</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1845</v>
+        <v>-0.1964</v>
       </c>
       <c r="U3" t="n">
         <v>0.4832</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1616</v>
+        <v>1.2852</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9064</v>
+        <v>0.9628</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2552</v>
+        <v>0.3224</v>
       </c>
       <c r="G4" t="n">
         <v>0.6935</v>
@@ -766,13 +766,13 @@
         <v>0.232</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2362</v>
+        <v>0.3598</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3486</v>
+        <v>0.405</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1125</v>
+        <v>-0.0452</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4593</v>
+        <v>0.5511</v>
       </c>
       <c r="E5" t="n">
-        <v>0.45</v>
+        <v>0.6427</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0092</v>
+        <v>-0.0916</v>
       </c>
       <c r="G5" t="n">
         <v>0.2123</v>
@@ -844,13 +844,13 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.539</v>
+        <v>-0.4472</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3734</v>
+        <v>-0.1808</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1656</v>
+        <v>-0.2664</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1418</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1925</v>
+        <v>0.1924</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8937</v>
+        <v>1.8601</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0862</v>
+        <v>-1.6676</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.8649</v>
+        <v>-1.3663</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4959</v>
+        <v>1.2268</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.369</v>
+        <v>-2.5931</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8525</v>
+        <v>1.1494</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0945</v>
+        <v>1.1126</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.947</v>
+        <v>0.0368</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0123</v>
+        <v>-2.5157</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5904</v>
+        <v>0.1141</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.422</v>
+        <v>-2.6299</v>
       </c>
       <c r="P6" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9739</v>
+        <v>0.0226</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6018</v>
+        <v>-0.3615</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3721</v>
+        <v>0.3842</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4665</v>
+        <v>1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.219</v>
+        <v>-0.6354</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5495</v>
+        <v>3.6449</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7685</v>
+        <v>-4.2804</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3663</v>
+        <v>-2.7651</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2268</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.5931</v>
+        <v>-1.8503</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1494</v>
+        <v>1.4452</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1126</v>
+        <v>0.6624</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0368</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.5157</v>
+        <v>-4.2103</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1141</v>
+        <v>-1.5771</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.6299</v>
+        <v>-2.6331</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3888</v>
+        <v>0.8797</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6721</v>
+        <v>0.0553</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2834</v>
+        <v>0.8244</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2794</v>
+        <v>-0.6392</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9674</v>
+        <v>-1.3413</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.2468</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.7651</v>
+        <v>-3.3271</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9147999999999999</v>
+        <v>0.3301</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8503</v>
+        <v>-3.6571</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4452</v>
+        <v>-1.8583</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6624</v>
+        <v>0.4271</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7828000000000001</v>
+        <v>-2.2854</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.2103</v>
+        <v>-1.4687</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5771</v>
+        <v>-0.097</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.6331</v>
+        <v>-1.3717</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2357</v>
+        <v>0.0795</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3778</v>
+        <v>-0.4676</v>
       </c>
       <c r="U8" t="n">
-        <v>0.858</v>
+        <v>0.5472</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1418</v>
+        <v>2.1444</v>
       </c>
       <c r="W8" t="n">
         <v>2.1444</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4599</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9939</v>
+        <v>1.3354</v>
       </c>
       <c r="F9" t="n">
-        <v>0.534</v>
+        <v>-2.0526</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.3271</v>
+        <v>-2.8649</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3301</v>
+        <v>-0.4959</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.6571</v>
+        <v>-2.369</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8583</v>
+        <v>-0.8525</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4271</v>
+        <v>0.0945</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.2854</v>
+        <v>-0.947</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4687</v>
+        <v>-2.0123</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.097</v>
+        <v>-0.5904</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3717</v>
+        <v>-1.422</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7411</v>
+        <v>0.4492</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1202</v>
+        <v>0.0435</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3791</v>
+        <v>0.4057</v>
       </c>
       <c r="V9" t="n">
-        <v>2.1444</v>
+        <v>1.4665</v>
       </c>
       <c r="W9" t="n">
         <v>2.1444</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. HOWARD</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2577</v>
+        <v>-2.6367</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1851</v>
+        <v>-0.0292</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0727</v>
+        <v>-2.6075</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3131</v>
+        <v>-4.9595</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5378</v>
+        <v>-3.2966</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.8509</v>
+        <v>-1.6629</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4979</v>
+        <v>-2.3472</v>
       </c>
       <c r="K10" t="n">
-        <v>1.6672</v>
+        <v>-2.7386</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.1651</v>
+        <v>0.3914</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8152</v>
+        <v>-2.6123</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1294</v>
+        <v>-0.5581</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6859</v>
+        <v>-2.0543</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6225000000000001</v>
+        <v>0.2506</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0455</v>
+        <v>-0.275</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4231</v>
+        <v>0.5256</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3943</v>
+        <v>1.6083</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6778999999999999</v>
+        <v>3.7527</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>M. HOWARD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5678</v>
+        <v>-2.939</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7251</v>
+        <v>-2.5639</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8427</v>
+        <v>-0.3751</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.9595</v>
+        <v>-1.3131</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.2966</v>
+        <v>1.5378</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6629</v>
+        <v>-2.8509</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.3472</v>
+        <v>-0.4979</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.7386</v>
+        <v>1.6672</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3914</v>
+        <v>-2.1651</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.6123</v>
+        <v>-0.8152</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5581</v>
+        <v>-0.1294</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.0543</v>
+        <v>-0.6859</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6805</v>
+        <v>-0.3038</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9709</v>
+        <v>-0.4244</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2904</v>
+        <v>0.1206</v>
       </c>
       <c r="V11" t="n">
-        <v>1.6083</v>
+        <v>-0.3943</v>
       </c>
       <c r="W11" t="n">
-        <v>3.7527</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.157</v>
+        <v>-4.4419</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3101</v>
+        <v>-2.5277</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8469</v>
+        <v>-1.9141</v>
       </c>
       <c r="G12" t="n">
         <v>-2.2949</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6818</v>
+        <v>0.0334</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0455</v>
+        <v>-0.2631</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3637</v>
+        <v>0.2965</v>
       </c>
       <c r="V12" t="n">
         <v>-0.7886</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.756600000000001</v>
+        <v>-4.263</v>
       </c>
       <c r="E13" t="n">
-        <v>6.133900000000001</v>
+        <v>7.627700000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.8907</v>
+        <v>-11.8905</v>
       </c>
       <c r="G13" t="n">
         <v>-16.7056</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6785000000000005</v>
+        <v>-0.6785000000000003</v>
       </c>
       <c r="I13" t="n">
         <v>-16.0271</v>
@@ -1459,7 +1459,7 @@
         <v>-12.6469</v>
       </c>
       <c r="P13" t="n">
-        <v>4.6391</v>
+        <v>4.639099999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-6.958600000000001</v>
@@ -1468,13 +1468,13 @@
         <v>11.5977</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4127999999999998</v>
+        <v>1.9066</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.0444</v>
+        <v>-1.5508</v>
       </c>
       <c r="U13" t="n">
-        <v>3.4574</v>
+        <v>3.4575</v>
       </c>
       <c r="V13" t="n">
         <v>5.897099999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.8546</v>
+        <v>7.5407</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6127</v>
+        <v>5.4332</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2419</v>
+        <v>2.1075</v>
       </c>
       <c r="G14" t="n">
         <v>3.1579</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8565</v>
+        <v>0.5425</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3135</v>
+        <v>0.134</v>
       </c>
       <c r="U14" t="n">
-        <v>0.543</v>
+        <v>0.4086</v>
       </c>
       <c r="V14" t="n">
         <v>2.6805</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0971</v>
+        <v>4.7706</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3909</v>
+        <v>2.8627</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7063</v>
+        <v>1.9079</v>
       </c>
       <c r="G15" t="n">
         <v>1.9677</v>
@@ -1624,13 +1624,13 @@
         <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7108</v>
+        <v>-0.0373</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9709</v>
+        <v>-0.4991</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2601</v>
+        <v>0.4617</v>
       </c>
       <c r="V15" t="n">
         <v>2.1444</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0554</v>
+        <v>3.1905</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7911</v>
+        <v>2.027</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2643</v>
+        <v>1.1635</v>
       </c>
       <c r="G16" t="n">
         <v>2.0845</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6374</v>
+        <v>-0.5023</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9709</v>
+        <v>-0.735</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3334</v>
+        <v>0.2326</v>
       </c>
       <c r="V16" t="n">
         <v>1.6083</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1468</v>
+        <v>1.8031</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4811</v>
+        <v>1.835</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3343</v>
+        <v>-0.0318</v>
       </c>
       <c r="G17" t="n">
         <v>5.1925</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1901</v>
+        <v>-0.5337</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9709</v>
+        <v>-0.617</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2192</v>
+        <v>0.0833</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5361</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5312</v>
+        <v>0.4135</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2037</v>
+        <v>1.6242</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6725</v>
+        <v>-1.2106</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2286</v>
+        <v>1.1282</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2809</v>
+        <v>-0.8894</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5095</v>
+        <v>2.0176</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9006</v>
+        <v>2.1546</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6995</v>
+        <v>-0.077</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2011</v>
+        <v>2.2317</v>
       </c>
       <c r="M18" t="n">
-        <v>0.328</v>
+        <v>-1.0264</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9804</v>
+        <v>-0.8123</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3084</v>
+        <v>-0.214</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7332</v>
+        <v>-0.1966</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3031</v>
+        <v>-0.5305</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4301</v>
+        <v>0.3339</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.3584</v>
+        <v>-1.214</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.3584</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3107</v>
+        <v>-0.1086</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0344</v>
+        <v>1.7319</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3451</v>
+        <v>-1.8405</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1282</v>
+        <v>2.2286</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8894</v>
+        <v>-0.2809</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0176</v>
+        <v>2.5095</v>
       </c>
       <c r="J19" t="n">
-        <v>2.1546</v>
+        <v>1.9006</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.077</v>
+        <v>0.6995</v>
       </c>
       <c r="L19" t="n">
-        <v>2.2317</v>
+        <v>1.2011</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0264</v>
+        <v>0.328</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8123</v>
+        <v>-0.9804</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.214</v>
+        <v>1.3084</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9208</v>
+        <v>0.0934</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1202</v>
+        <v>-0.1687</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1994</v>
+        <v>0.2621</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.214</v>
+        <v>-3.3584</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.214</v>
+        <v>-3.3584</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0087</v>
+        <v>-0.9079</v>
       </c>
       <c r="E20" t="n">
         <v>0.4502</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4589</v>
+        <v>-1.3581</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7025</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3062</v>
+        <v>-0.2054</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3734</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0672</v>
+        <v>0.168</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3251</v>
+        <v>-1.2407</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.801</v>
+        <v>-1.683</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4759</v>
+        <v>0.4423</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2201</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.105</v>
+        <v>-0.0206</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1937</v>
+        <v>0.1601</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5521</v>
+        <v>-1.9732</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2824</v>
+        <v>-0.6363</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2697</v>
+        <v>-1.3369</v>
       </c>
       <c r="G22" t="n">
         <v>0.4823</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5017</v>
+        <v>0.0806</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4876</v>
+        <v>0.1338</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0141</v>
+        <v>-0.0532</v>
       </c>
       <c r="V22" t="n">
         <v>-1.6083</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3993</v>
+        <v>-2.6009</v>
       </c>
       <c r="E24" t="n">
         <v>-1.4964</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9029</v>
+        <v>-1.1046</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4063</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.239</v>
+        <v>0.0373</v>
       </c>
       <c r="T24" t="n">
         <v>-0.3734</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.4107</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.0506</v>
+        <v>-2.8483</v>
       </c>
       <c r="E25" t="n">
-        <v>0.444</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.4946</v>
+        <v>-3.5282</v>
       </c>
       <c r="G25" t="n">
         <v>2.7684</v>
@@ -2404,13 +2404,13 @@
         <v>0.9278</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2016</v>
+        <v>0.4039</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3339</v>
+        <v>-0.098</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5355</v>
+        <v>0.5019</v>
       </c>
       <c r="V25" t="n">
         <v>-3.4691</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>5.7565</v>
+        <v>5.7567</v>
       </c>
       <c r="E26" t="n">
-        <v>11.8906</v>
+        <v>11.8907</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.134000000000001</v>
+        <v>-6.1339</v>
       </c>
       <c r="G26" t="n">
         <v>16.7057</v>
@@ -2482,7 +2482,7 @@
         <v>6.9588</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4129999999999997</v>
+        <v>-0.4129000000000001</v>
       </c>
       <c r="T26" t="n">
         <v>-3.4575</v>
